--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/98.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/98.xlsx
@@ -426,13 +426,13 @@
         <v>-14.96915577837801</v>
       </c>
       <c r="E2">
-        <v>-10.09952707741224</v>
+        <v>-8.982868785756837</v>
       </c>
       <c r="F2">
-        <v>-1.843912851183095</v>
+        <v>-2.567556390185882</v>
       </c>
       <c r="G2">
-        <v>-9.837677864986301</v>
+        <v>-9.241369160270617</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-14.49331265657169</v>
       </c>
       <c r="E3">
-        <v>-10.34519679232836</v>
+        <v>-9.382447746771646</v>
       </c>
       <c r="F3">
-        <v>-1.572091543261063</v>
+        <v>-3.068943156445741</v>
       </c>
       <c r="G3">
-        <v>-9.63622785837611</v>
+        <v>-9.083393237682134</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-14.07740255143561</v>
       </c>
       <c r="E4">
-        <v>-11.0000186623115</v>
+        <v>-11.03483809895648</v>
       </c>
       <c r="F4">
-        <v>-1.556477646085695</v>
+        <v>-2.498045596314767</v>
       </c>
       <c r="G4">
-        <v>-9.547058314275839</v>
+        <v>-8.949852451719014</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-13.77231613658881</v>
       </c>
       <c r="E5">
-        <v>-11.2401319396202</v>
+        <v>-11.52425745580946</v>
       </c>
       <c r="F5">
-        <v>-1.406668229656807</v>
+        <v>-2.663390215015756</v>
       </c>
       <c r="G5">
-        <v>-9.429874933822257</v>
+        <v>-9.198772370816815</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-13.56725628106718</v>
       </c>
       <c r="E6">
-        <v>-12.01466401999611</v>
+        <v>-11.12893526036186</v>
       </c>
       <c r="F6">
-        <v>-1.169612673262867</v>
+        <v>-2.428146298131739</v>
       </c>
       <c r="G6">
-        <v>-9.151756003068085</v>
+        <v>-8.548468668355618</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-13.46015312250729</v>
       </c>
       <c r="E7">
-        <v>-13.0999037589863</v>
+        <v>-11.74569077783652</v>
       </c>
       <c r="F7">
-        <v>-1.126139123596546</v>
+        <v>-2.419234721612422</v>
       </c>
       <c r="G7">
-        <v>-8.599593423118582</v>
+        <v>-8.720729594946055</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-13.44726008119121</v>
       </c>
       <c r="E8">
-        <v>-13.38540140279988</v>
+        <v>-12.27778194526378</v>
       </c>
       <c r="F8">
-        <v>-1.18172754652881</v>
+        <v>-2.233491555617495</v>
       </c>
       <c r="G8">
-        <v>-8.472955124604843</v>
+        <v>-9.112936546074591</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-13.51716208125445</v>
       </c>
       <c r="E9">
-        <v>-14.54224990127335</v>
+        <v>-13.85183422558992</v>
       </c>
       <c r="F9">
-        <v>-1.338178812793344</v>
+        <v>-1.983011477093785</v>
       </c>
       <c r="G9">
-        <v>-8.134008230112102</v>
+        <v>-8.298873397967807</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-13.66109427545555</v>
       </c>
       <c r="E10">
-        <v>-15.04470220632041</v>
+        <v>-14.58103175267504</v>
       </c>
       <c r="F10">
-        <v>-1.150837726078416</v>
+        <v>-2.269542104987329</v>
       </c>
       <c r="G10">
-        <v>-7.940477048431847</v>
+        <v>-8.34373791111601</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-13.85883491261801</v>
       </c>
       <c r="E11">
-        <v>-15.69558883239088</v>
+        <v>-14.498355402717</v>
       </c>
       <c r="F11">
-        <v>-0.8128182655290639</v>
+        <v>-1.767302120302586</v>
       </c>
       <c r="G11">
-        <v>-7.118273268843994</v>
+        <v>-7.688180372883989</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-14.10030009123135</v>
       </c>
       <c r="E12">
-        <v>-16.20918118349681</v>
+        <v>-15.47439099101222</v>
       </c>
       <c r="F12">
-        <v>-0.7447016139968605</v>
+        <v>-1.429996712454447</v>
       </c>
       <c r="G12">
-        <v>-7.548657431131406</v>
+        <v>-7.005089027401851</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-14.37003653419996</v>
       </c>
       <c r="E13">
-        <v>-17.52698523362492</v>
+        <v>-15.10200551641347</v>
       </c>
       <c r="F13">
-        <v>-0.4750937037751082</v>
+        <v>-1.724627945179966</v>
       </c>
       <c r="G13">
-        <v>-6.374489691990397</v>
+        <v>-6.542609126111206</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-14.67138724885895</v>
       </c>
       <c r="E14">
-        <v>-18.27524310780832</v>
+        <v>-16.1987838071752</v>
       </c>
       <c r="F14">
-        <v>-0.7075816423100119</v>
+        <v>-1.220718800178582</v>
       </c>
       <c r="G14">
-        <v>-6.835946634709408</v>
+        <v>-6.369513942044873</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-15.00859481692571</v>
       </c>
       <c r="E15">
-        <v>-18.41608770639488</v>
+        <v>-17.93554868707094</v>
       </c>
       <c r="F15">
-        <v>-0.1808509753615014</v>
+        <v>-1.165815437088434</v>
       </c>
       <c r="G15">
-        <v>-5.940242123058656</v>
+        <v>-6.545201283268455</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-15.39480137641178</v>
       </c>
       <c r="E16">
-        <v>-18.93488327413562</v>
+        <v>-17.63580899250324</v>
       </c>
       <c r="F16">
-        <v>0.005300575763006284</v>
+        <v>-0.6689068250081085</v>
       </c>
       <c r="G16">
-        <v>-6.162022189825512</v>
+        <v>-6.142754814786954</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-15.83696012529371</v>
       </c>
       <c r="E17">
-        <v>-21.14294908637966</v>
+        <v>-19.79130827846624</v>
       </c>
       <c r="F17">
-        <v>0.4140626125114363</v>
+        <v>-0.5694911395285287</v>
       </c>
       <c r="G17">
-        <v>-6.109010424105162</v>
+        <v>-6.491391676073142</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-16.33018294986977</v>
       </c>
       <c r="E18">
-        <v>-21.16343590279036</v>
+        <v>-20.14426659957208</v>
       </c>
       <c r="F18">
-        <v>0.6289436018998364</v>
+        <v>-0.1343447726335316</v>
       </c>
       <c r="G18">
-        <v>-6.190913320746732</v>
+        <v>-6.170904383507376</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-16.85838389199051</v>
       </c>
       <c r="E19">
-        <v>-21.87026276827758</v>
+        <v>-20.39764830572326</v>
       </c>
       <c r="F19">
-        <v>1.153344899711675</v>
+        <v>0.2813374453978855</v>
       </c>
       <c r="G19">
-        <v>-5.574910180617924</v>
+        <v>-6.0581472024398</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-17.38850732788883</v>
       </c>
       <c r="E20">
-        <v>-22.47644429894434</v>
+        <v>-21.36718100534346</v>
       </c>
       <c r="F20">
-        <v>1.563259195517399</v>
+        <v>0.6967852354543104</v>
       </c>
       <c r="G20">
-        <v>-5.788347672625815</v>
+        <v>-6.20436737781833</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-17.89163403144446</v>
       </c>
       <c r="E21">
-        <v>-22.96776561488054</v>
+        <v>-21.24549185180934</v>
       </c>
       <c r="F21">
-        <v>1.719557213812415</v>
+        <v>0.9415429519594803</v>
       </c>
       <c r="G21">
-        <v>-5.667082389522312</v>
+        <v>-5.955798376547691</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-18.33347508678642</v>
       </c>
       <c r="E22">
-        <v>-23.16856268085465</v>
+        <v>-22.60221360755937</v>
       </c>
       <c r="F22">
-        <v>2.002512607995476</v>
+        <v>0.9101378869845455</v>
       </c>
       <c r="G22">
-        <v>-5.860292448285257</v>
+        <v>-6.376197933488661</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-18.6944218365119</v>
       </c>
       <c r="E23">
-        <v>-24.57181450703349</v>
+        <v>-22.12765670239956</v>
       </c>
       <c r="F23">
-        <v>2.478462696417571</v>
+        <v>1.390541278564091</v>
       </c>
       <c r="G23">
-        <v>-6.505782617532353</v>
+        <v>-6.723351670373256</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-18.94982494167946</v>
       </c>
       <c r="E24">
-        <v>-24.44959552204048</v>
+        <v>-22.5214663875286</v>
       </c>
       <c r="F24">
-        <v>2.549523365699324</v>
+        <v>1.662428027510944</v>
       </c>
       <c r="G24">
-        <v>-6.012455052906779</v>
+        <v>-6.468578706762024</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-19.09181941684023</v>
       </c>
       <c r="E25">
-        <v>-24.71180775250661</v>
+        <v>-23.35079753187133</v>
       </c>
       <c r="F25">
-        <v>2.86941731910802</v>
+        <v>1.924162305569088</v>
       </c>
       <c r="G25">
-        <v>-6.500969084318253</v>
+        <v>-6.037260970632538</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-19.1047549464361</v>
       </c>
       <c r="E26">
-        <v>-25.0598345654181</v>
+        <v>-22.06382333278744</v>
       </c>
       <c r="F26">
-        <v>2.692126814091259</v>
+        <v>1.777143658920231</v>
       </c>
       <c r="G26">
-        <v>-6.956606087979225</v>
+        <v>-6.904024693178981</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-18.99145750227309</v>
       </c>
       <c r="E27">
-        <v>-25.77104499374476</v>
+        <v>-22.31094668786002</v>
       </c>
       <c r="F27">
-        <v>2.716624951661651</v>
+        <v>1.954237012495126</v>
       </c>
       <c r="G27">
-        <v>-6.492275591732127</v>
+        <v>-7.118114362658109</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-18.74913972075733</v>
       </c>
       <c r="E28">
-        <v>-24.16844521327426</v>
+        <v>-22.44799642522815</v>
       </c>
       <c r="F28">
-        <v>2.885189434457323</v>
+        <v>1.714603576743674</v>
       </c>
       <c r="G28">
-        <v>-6.946399676081652</v>
+        <v>-7.143701569131136</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-18.39432441711623</v>
       </c>
       <c r="E29">
-        <v>-23.67031307243052</v>
+        <v>-22.78542208048769</v>
       </c>
       <c r="F29">
-        <v>2.822178839595975</v>
+        <v>2.26324124802662</v>
       </c>
       <c r="G29">
-        <v>-6.948323103039969</v>
+        <v>-6.812594046475389</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-17.93912879457823</v>
       </c>
       <c r="E30">
-        <v>-24.00892065940606</v>
+        <v>-22.32459550851914</v>
       </c>
       <c r="F30">
-        <v>2.924091224427593</v>
+        <v>1.67836084613639</v>
       </c>
       <c r="G30">
-        <v>-6.92215324055203</v>
+        <v>-6.662080093532425</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-17.40848581812744</v>
       </c>
       <c r="E31">
-        <v>-24.03278571742648</v>
+        <v>-21.73362965051816</v>
       </c>
       <c r="F31">
-        <v>2.784093819884865</v>
+        <v>1.894582962349923</v>
       </c>
       <c r="G31">
-        <v>-6.811150648620266</v>
+        <v>-6.880003374746029</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-16.82284170525748</v>
       </c>
       <c r="E32">
-        <v>-23.3938814335803</v>
+        <v>-22.15474150543944</v>
       </c>
       <c r="F32">
-        <v>2.5602871717313</v>
+        <v>1.774965052650868</v>
       </c>
       <c r="G32">
-        <v>-6.020665205844171</v>
+        <v>-6.841885753406861</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-16.2111456430378</v>
       </c>
       <c r="E33">
-        <v>-22.65758325925115</v>
+        <v>-21.34674400214685</v>
       </c>
       <c r="F33">
-        <v>2.053629503687428</v>
+        <v>1.587454150618367</v>
       </c>
       <c r="G33">
-        <v>-6.304534554200058</v>
+        <v>-6.25896820539753</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-15.59395257698421</v>
       </c>
       <c r="E34">
-        <v>-22.5699391733067</v>
+        <v>-21.58200728379334</v>
       </c>
       <c r="F34">
-        <v>2.431046946281327</v>
+        <v>1.75642453344141</v>
       </c>
       <c r="G34">
-        <v>-5.735276317085759</v>
+        <v>-6.275845366556734</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-14.99797711707316</v>
       </c>
       <c r="E35">
-        <v>-22.32734429224179</v>
+        <v>-20.73147835262071</v>
       </c>
       <c r="F35">
-        <v>2.524960615471513</v>
+        <v>1.789203031570186</v>
       </c>
       <c r="G35">
-        <v>-6.837774055847086</v>
+        <v>-5.729429893663406</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-14.43673384194763</v>
       </c>
       <c r="E36">
-        <v>-22.04004431577316</v>
+        <v>-19.64246186630812</v>
       </c>
       <c r="F36">
-        <v>2.260010615155702</v>
+        <v>1.270398183931662</v>
       </c>
       <c r="G36">
-        <v>-5.780203730599209</v>
+        <v>-6.456799785733296</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-13.92940564219603</v>
       </c>
       <c r="E37">
-        <v>-21.22281778245294</v>
+        <v>-19.33700723754274</v>
       </c>
       <c r="F37">
-        <v>2.185063246020014</v>
+        <v>1.212448913901419</v>
       </c>
       <c r="G37">
-        <v>-5.346618270775322</v>
+        <v>-5.733468759221317</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-13.47950425192612</v>
       </c>
       <c r="E38">
-        <v>-20.88992512967508</v>
+        <v>-19.32663703206518</v>
       </c>
       <c r="F38">
-        <v>2.305453194138478</v>
+        <v>1.012640069406956</v>
       </c>
       <c r="G38">
-        <v>-5.709040243687035</v>
+        <v>-5.780478505878968</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-13.09626613451422</v>
       </c>
       <c r="E39">
-        <v>-20.63037564192546</v>
+        <v>-19.45791296507353</v>
       </c>
       <c r="F39">
-        <v>1.832574692045963</v>
+        <v>0.9656037115411947</v>
       </c>
       <c r="G39">
-        <v>-4.834026641656728</v>
+        <v>-5.562353281387468</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-12.77369800192793</v>
       </c>
       <c r="E40">
-        <v>-20.1995366248357</v>
+        <v>-18.76107138477322</v>
       </c>
       <c r="F40">
-        <v>2.174884267374414</v>
+        <v>0.6977229473542794</v>
       </c>
       <c r="G40">
-        <v>-4.803218704868271</v>
+        <v>-5.262288744253467</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-12.51511565000559</v>
       </c>
       <c r="E41">
-        <v>-19.45977416789069</v>
+        <v>-17.37842411532928</v>
       </c>
       <c r="F41">
-        <v>2.019762530791373</v>
+        <v>0.9694390526161565</v>
       </c>
       <c r="G41">
-        <v>-4.743122371693881</v>
+        <v>-4.849496820961742</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-12.30565280172376</v>
       </c>
       <c r="E42">
-        <v>-18.73466132436048</v>
+        <v>-17.93362408561768</v>
       </c>
       <c r="F42">
-        <v>1.626014653218684</v>
+        <v>0.9979895635210442</v>
       </c>
       <c r="G42">
-        <v>-4.425968798486162</v>
+        <v>-4.875517708900414</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-12.14172301075621</v>
       </c>
       <c r="E43">
-        <v>-18.53610132454616</v>
+        <v>-17.13433936631585</v>
       </c>
       <c r="F43">
-        <v>1.849259668273151</v>
+        <v>0.5237840168492448</v>
       </c>
       <c r="G43">
-        <v>-4.56392916274421</v>
+        <v>-4.661927931797716</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-11.99946296897673</v>
       </c>
       <c r="E44">
-        <v>-17.80032845320191</v>
+        <v>-17.29812521422527</v>
       </c>
       <c r="F44">
-        <v>1.293165033630203</v>
+        <v>0.5735862934729539</v>
       </c>
       <c r="G44">
-        <v>-4.153838644612531</v>
+        <v>-4.10692490377552</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-11.8696499423461</v>
       </c>
       <c r="E45">
-        <v>-17.48461683080915</v>
+        <v>-16.65725557265976</v>
       </c>
       <c r="F45">
-        <v>1.300234321045694</v>
+        <v>0.1558894859179284</v>
       </c>
       <c r="G45">
-        <v>-4.097575923172617</v>
+        <v>-4.328807597454092</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-11.72412385655944</v>
       </c>
       <c r="E46">
-        <v>-17.32407789876323</v>
+        <v>-14.86361305922768</v>
       </c>
       <c r="F46">
-        <v>1.208391570362507</v>
+        <v>0.2175788347718104</v>
       </c>
       <c r="G46">
-        <v>-4.030510891638062</v>
+        <v>-3.748240536777643</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-11.55343868627366</v>
       </c>
       <c r="E47">
-        <v>-16.53191646907546</v>
+        <v>-14.96947066763098</v>
       </c>
       <c r="F47">
-        <v>1.088523493707808</v>
+        <v>-0.2182277409432179</v>
       </c>
       <c r="G47">
-        <v>-3.448202484007956</v>
+        <v>-3.859610599264265</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-11.33370236536919</v>
       </c>
       <c r="E48">
-        <v>-16.76965229753014</v>
+        <v>-15.04541770521362</v>
       </c>
       <c r="F48">
-        <v>0.8574967952714425</v>
+        <v>0.3332064986915794</v>
       </c>
       <c r="G48">
-        <v>-3.299131928920114</v>
+        <v>-2.723060589085995</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-11.06375709862061</v>
       </c>
       <c r="E49">
-        <v>-15.65679339556717</v>
+        <v>-14.55147893130098</v>
       </c>
       <c r="F49">
-        <v>0.604238372478744</v>
+        <v>-0.3252378987716636</v>
       </c>
       <c r="G49">
-        <v>-4.384669742883754</v>
+        <v>-3.423307181552637</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-10.73411206668393</v>
       </c>
       <c r="E50">
-        <v>-15.90480886001926</v>
+        <v>-14.06939570234043</v>
       </c>
       <c r="F50">
-        <v>0.5444766345711765</v>
+        <v>-0.2848897793161053</v>
       </c>
       <c r="G50">
-        <v>-4.215077115997969</v>
+        <v>-3.85309544564298</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-10.35494577224268</v>
       </c>
       <c r="E51">
-        <v>-15.14705024736777</v>
+        <v>-13.52792153676928</v>
       </c>
       <c r="F51">
-        <v>0.3770354179737012</v>
+        <v>-0.588718375314908</v>
       </c>
       <c r="G51">
-        <v>-4.106130372846094</v>
+        <v>-3.348740453826093</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-9.928544101838929</v>
       </c>
       <c r="E52">
-        <v>-14.20464763552752</v>
+        <v>-12.8230736144234</v>
       </c>
       <c r="F52">
-        <v>0.5035196650745606</v>
+        <v>-0.8144990229893441</v>
       </c>
       <c r="G52">
-        <v>-3.639035571073705</v>
+        <v>-3.534998366956568</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-9.4709791729753</v>
       </c>
       <c r="E53">
-        <v>-13.70972618275522</v>
+        <v>-13.40133710283287</v>
       </c>
       <c r="F53">
-        <v>0.03516736247094246</v>
+        <v>-0.7072328996334333</v>
       </c>
       <c r="G53">
-        <v>-3.816503985797415</v>
+        <v>-3.676719510947228</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-8.989949815857718</v>
       </c>
       <c r="E54">
-        <v>-13.9673012558375</v>
+        <v>-12.44855070009303</v>
       </c>
       <c r="F54">
-        <v>0.2625856925007131</v>
+        <v>-0.7365198291594098</v>
       </c>
       <c r="G54">
-        <v>-3.748319989870585</v>
+        <v>-4.220857328509537</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-8.50227308548261</v>
       </c>
       <c r="E55">
-        <v>-13.76743705550897</v>
+        <v>-12.45672912415088</v>
       </c>
       <c r="F55">
-        <v>0.2327404433452497</v>
+        <v>-0.2167656724772768</v>
       </c>
       <c r="G55">
-        <v>-4.031096858198513</v>
+        <v>-3.69724489329071</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-8.016504792341772</v>
       </c>
       <c r="E56">
-        <v>-12.46097230429607</v>
+        <v>-12.90743002823828</v>
       </c>
       <c r="F56">
-        <v>-0.09395274970562488</v>
+        <v>-0.7419655164654138</v>
       </c>
       <c r="G56">
-        <v>-4.564551545305593</v>
+        <v>-3.914615313399256</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-7.546225364683766</v>
       </c>
       <c r="E57">
-        <v>-11.9056138374174</v>
+        <v>-12.38929561770266</v>
       </c>
       <c r="F57">
-        <v>-0.04226013866872733</v>
+        <v>-0.7295143260339344</v>
       </c>
       <c r="G57">
-        <v>-4.468532482484572</v>
+        <v>-3.820817626635086</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-7.097914154099858</v>
       </c>
       <c r="E58">
-        <v>-12.46190969841566</v>
+        <v>-10.88880839763113</v>
       </c>
       <c r="F58">
-        <v>0.4395630746392163</v>
+        <v>-0.8527646267942645</v>
       </c>
       <c r="G58">
-        <v>-4.405549353599937</v>
+        <v>-4.412547846869956</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-6.68010972527352</v>
       </c>
       <c r="E59">
-        <v>-12.3235467035853</v>
+        <v>-10.94565886032342</v>
       </c>
       <c r="F59">
-        <v>-0.02601833900203742</v>
+        <v>-0.7928198196906782</v>
       </c>
       <c r="G59">
-        <v>-4.501637937877284</v>
+        <v>-4.348972130333792</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-6.296165003347766</v>
       </c>
       <c r="E60">
-        <v>-11.90090422444942</v>
+        <v>-10.64399456430246</v>
       </c>
       <c r="F60">
-        <v>0.1599211500673536</v>
+        <v>-0.8757228293628527</v>
       </c>
       <c r="G60">
-        <v>-4.487210580417139</v>
+        <v>-3.974287896744619</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-5.9488809971696</v>
       </c>
       <c r="E61">
-        <v>-11.94382057262012</v>
+        <v>-11.00558415686693</v>
       </c>
       <c r="F61">
-        <v>-0.05191724585056397</v>
+        <v>-0.8273146950780552</v>
       </c>
       <c r="G61">
-        <v>-4.930651534311437</v>
+        <v>-4.124848197325133</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-5.638089665943113</v>
       </c>
       <c r="E62">
-        <v>-11.71542245756925</v>
+        <v>-11.03776802163944</v>
       </c>
       <c r="F62">
-        <v>-0.0966051821293889</v>
+        <v>-0.7434458090142164</v>
       </c>
       <c r="G62">
-        <v>-5.178081707916565</v>
+        <v>-4.311569586831107</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-5.362900011183632</v>
       </c>
       <c r="E63">
-        <v>-10.92624982072655</v>
+        <v>-11.0780669118337</v>
       </c>
       <c r="F63">
-        <v>-0.2023056910940086</v>
+        <v>-0.7761075073391982</v>
       </c>
       <c r="G63">
-        <v>-5.070896174991582</v>
+        <v>-3.952133725995816</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-5.122496490722554</v>
       </c>
       <c r="E64">
-        <v>-10.67838379591671</v>
+        <v>-10.79474746401781</v>
       </c>
       <c r="F64">
-        <v>-0.3911858844433379</v>
+        <v>-0.7553900385951825</v>
       </c>
       <c r="G64">
-        <v>-4.992409761346541</v>
+        <v>-4.442620842548696</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-4.914983169238799</v>
       </c>
       <c r="E65">
-        <v>-10.86575393645808</v>
+        <v>-10.66577199580535</v>
       </c>
       <c r="F65">
-        <v>-0.4555550018452763</v>
+        <v>-0.8022930293090933</v>
       </c>
       <c r="G65">
-        <v>-4.950859104283148</v>
+        <v>-4.144926656020814</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-4.739530389214541</v>
       </c>
       <c r="E66">
-        <v>-10.75678979488552</v>
+        <v>-10.53873924294218</v>
       </c>
       <c r="F66">
-        <v>-0.4249923865189885</v>
+        <v>-1.08725058750472</v>
       </c>
       <c r="G66">
-        <v>-4.590284415782348</v>
+        <v>-3.930850228723842</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-4.592145976672438</v>
       </c>
       <c r="E67">
-        <v>-10.36613192766582</v>
+        <v>-10.58000722657408</v>
       </c>
       <c r="F67">
-        <v>-0.3772792524851398</v>
+        <v>-0.9151961928410547</v>
       </c>
       <c r="G67">
-        <v>-5.223095195614036</v>
+        <v>-4.061990869170991</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-4.469365328254745</v>
       </c>
       <c r="E68">
-        <v>-10.0134815427925</v>
+        <v>-10.94306857319104</v>
       </c>
       <c r="F68">
-        <v>-0.5225111106461575</v>
+        <v>-1.508471269991255</v>
       </c>
       <c r="G68">
-        <v>-4.721272771134691</v>
+        <v>-4.156513565408262</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-4.36378861276578</v>
       </c>
       <c r="E69">
-        <v>-9.365547481775021</v>
+        <v>-10.66182316647066</v>
       </c>
       <c r="F69">
-        <v>-0.456679924778278</v>
+        <v>-1.229478785463187</v>
       </c>
       <c r="G69">
-        <v>-4.348187531040986</v>
+        <v>-4.120931821952175</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-4.269433415749116</v>
       </c>
       <c r="E70">
-        <v>-10.91116094533299</v>
+        <v>-10.47680330393927</v>
       </c>
       <c r="F70">
-        <v>-0.51627433247048</v>
+        <v>-1.416144752744833</v>
       </c>
       <c r="G70">
-        <v>-4.708252395528738</v>
+        <v>-3.754000886015975</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-4.17668885855792</v>
       </c>
       <c r="E71">
-        <v>-10.69090955502193</v>
+        <v>-11.40724621592526</v>
       </c>
       <c r="F71">
-        <v>-0.5833414425033364</v>
+        <v>-1.24541657429305</v>
       </c>
       <c r="G71">
-        <v>-4.165412311817823</v>
+        <v>-4.153054045319724</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-4.080853708406841</v>
       </c>
       <c r="E72">
-        <v>-10.41272539673074</v>
+        <v>-11.31860586569912</v>
       </c>
       <c r="F72">
-        <v>-0.6452113754510287</v>
+        <v>-1.086795813800584</v>
       </c>
       <c r="G72">
-        <v>-3.93894451256736</v>
+        <v>-3.945807273470269</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-3.973139914208944</v>
       </c>
       <c r="E73">
-        <v>-10.79619204722626</v>
+        <v>-11.03141457260668</v>
       </c>
       <c r="F73">
-        <v>-0.5480223415501739</v>
+        <v>-1.406509183115469</v>
       </c>
       <c r="G73">
-        <v>-3.421195053498582</v>
+        <v>-3.520249886579115</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.851284529406312</v>
       </c>
       <c r="E74">
-        <v>-12.20168093956488</v>
+        <v>-11.88450662006765</v>
       </c>
       <c r="F74">
-        <v>-0.6943708389701654</v>
+        <v>-1.626657760818272</v>
       </c>
       <c r="G74">
-        <v>-3.582405379078931</v>
+        <v>-3.967401962022935</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.710589681112915</v>
       </c>
       <c r="E75">
-        <v>-11.94012533782986</v>
+        <v>-11.46615713429105</v>
       </c>
       <c r="F75">
-        <v>-0.9607696538734724</v>
+        <v>-1.723840167779904</v>
       </c>
       <c r="G75">
-        <v>-3.218629393041657</v>
+        <v>-3.262302109795722</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.553342388899465</v>
       </c>
       <c r="E76">
-        <v>-11.3243796700589</v>
+        <v>-12.16625468740288</v>
       </c>
       <c r="F76">
-        <v>-1.184069341176524</v>
+        <v>-1.624926472946421</v>
       </c>
       <c r="G76">
-        <v>-3.28484030382708</v>
+        <v>-3.759860551620485</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.379296475746706</v>
       </c>
       <c r="E77">
-        <v>-11.63596585263067</v>
+        <v>-12.2740731250515</v>
       </c>
       <c r="F77">
-        <v>-1.127395756946593</v>
+        <v>-1.770477252557516</v>
       </c>
       <c r="G77">
-        <v>-3.064831378923735</v>
+        <v>-2.830325575103921</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.195698528787605</v>
       </c>
       <c r="E78">
-        <v>-12.76402684183739</v>
+        <v>-13.25875357022736</v>
       </c>
       <c r="F78">
-        <v>-1.208571620583931</v>
+        <v>-1.771782759584328</v>
       </c>
       <c r="G78">
-        <v>-2.725927521523004</v>
+        <v>-2.933247125374323</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.006733176514489</v>
       </c>
       <c r="E79">
-        <v>-12.79871042426213</v>
+        <v>-13.2570055792604</v>
       </c>
       <c r="F79">
-        <v>-1.085269132677224</v>
+        <v>-1.888013474973335</v>
       </c>
       <c r="G79">
-        <v>-2.117488977951431</v>
+        <v>-2.27811333697133</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-2.822992372291457</v>
       </c>
       <c r="E80">
-        <v>-13.88077570297294</v>
+        <v>-13.93291655269726</v>
       </c>
       <c r="F80">
-        <v>-1.335996064686967</v>
+        <v>-2.145074104144884</v>
       </c>
       <c r="G80">
-        <v>-2.189549622704747</v>
+        <v>-2.346711151090568</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-2.651036950755946</v>
       </c>
       <c r="E81">
-        <v>-14.10552386797362</v>
+        <v>-14.45118681745311</v>
       </c>
       <c r="F81">
-        <v>-1.5012942948134</v>
+        <v>-2.0147064706597</v>
       </c>
       <c r="G81">
-        <v>-1.793144899832415</v>
+        <v>-2.029772763342902</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.50303222926188</v>
       </c>
       <c r="E82">
-        <v>-14.97813363840765</v>
+        <v>-15.28328485941452</v>
       </c>
       <c r="F82">
-        <v>-1.45207767394347</v>
+        <v>-2.406025575007381</v>
       </c>
       <c r="G82">
-        <v>-1.535250091777651</v>
+        <v>-2.269830352032074</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-2.389015440111168</v>
       </c>
       <c r="E83">
-        <v>-15.78664285926311</v>
+        <v>-16.35118959990335</v>
       </c>
       <c r="F83">
-        <v>-1.593236449584923</v>
+        <v>-2.28468051927349</v>
       </c>
       <c r="G83">
-        <v>-0.8613653734402256</v>
+        <v>-1.163062009525087</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-2.321633541278429</v>
       </c>
       <c r="E84">
-        <v>-16.7870461661936</v>
+        <v>-17.10741305986624</v>
       </c>
       <c r="F84">
-        <v>-1.701295320545313</v>
+        <v>-2.705914455638469</v>
       </c>
       <c r="G84">
-        <v>-1.081764942717205</v>
+        <v>-1.152014719060539</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-2.313612538062982</v>
       </c>
       <c r="E85">
-        <v>-17.15987995971911</v>
+        <v>-17.48453531827701</v>
       </c>
       <c r="F85">
-        <v>-1.824357581905207</v>
+        <v>-2.78056361250915</v>
       </c>
       <c r="G85">
-        <v>-0.3527430884232182</v>
+        <v>-1.280682381989853</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-2.375586545684034</v>
       </c>
       <c r="E86">
-        <v>-19.01434440754821</v>
+        <v>-19.10068882145247</v>
       </c>
       <c r="F86">
-        <v>-2.077384061825122</v>
+        <v>-3.043224005323622</v>
       </c>
       <c r="G86">
-        <v>-0.2358013777940028</v>
+        <v>-0.5675445251932899</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-2.520660362722786</v>
       </c>
       <c r="E87">
-        <v>-20.2856138587735</v>
+        <v>-19.33489696865517</v>
       </c>
       <c r="F87">
-        <v>-2.318864756884817</v>
+        <v>-2.641966148877153</v>
       </c>
       <c r="G87">
-        <v>-0.7090604153605153</v>
+        <v>-1.35155785144011</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-2.754335237715667</v>
       </c>
       <c r="E88">
-        <v>-21.69576255086601</v>
+        <v>-21.28780138446301</v>
       </c>
       <c r="F88">
-        <v>-1.993019812054409</v>
+        <v>-2.873411172851932</v>
       </c>
       <c r="G88">
-        <v>-0.7052433563537356</v>
+        <v>-0.9410270307517081</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-3.087421882089836</v>
       </c>
       <c r="E89">
-        <v>-22.66969692722167</v>
+        <v>-22.1611538246343</v>
       </c>
       <c r="F89">
-        <v>-2.247831423727356</v>
+        <v>-3.236825892868909</v>
       </c>
       <c r="G89">
-        <v>-0.7874607548215355</v>
+        <v>-1.037463222310678</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-3.516204434473202</v>
       </c>
       <c r="E90">
-        <v>-25.09332263070483</v>
+        <v>-23.9453001280723</v>
       </c>
       <c r="F90">
-        <v>-2.748654900153312</v>
+        <v>-2.99794212961699</v>
       </c>
       <c r="G90">
-        <v>-0.5706796118189796</v>
+        <v>-0.4546218168487497</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-4.046413347092092</v>
       </c>
       <c r="E91">
-        <v>-25.64200159842218</v>
+        <v>-26.08395801920077</v>
       </c>
       <c r="F91">
-        <v>-2.507412774905624</v>
+        <v>-3.424155382440198</v>
       </c>
       <c r="G91">
-        <v>-0.729675182433557</v>
+        <v>-0.9386831645099041</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-4.66417002024111</v>
       </c>
       <c r="E92">
-        <v>-27.36626336158275</v>
+        <v>-27.1860527384475</v>
       </c>
       <c r="F92">
-        <v>-2.543426047742332</v>
+        <v>-3.4130304082206</v>
       </c>
       <c r="G92">
-        <v>-0.6362085502233136</v>
+        <v>-1.058084610474798</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-5.370897646112629</v>
       </c>
       <c r="E93">
-        <v>-29.44050370995211</v>
+        <v>-29.31642805061595</v>
       </c>
       <c r="F93">
-        <v>-2.48140535192733</v>
+        <v>-3.604288016015964</v>
       </c>
       <c r="G93">
-        <v>-1.406344069569509</v>
+        <v>-1.450337909240884</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-6.145428549520136</v>
       </c>
       <c r="E94">
-        <v>-31.88265087212663</v>
+        <v>-30.64112896665773</v>
       </c>
       <c r="F94">
-        <v>-2.418161157458394</v>
+        <v>-3.850433247920823</v>
       </c>
       <c r="G94">
-        <v>-1.936643806777664</v>
+        <v>-1.955427842167489</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-6.982251729327961</v>
       </c>
       <c r="E95">
-        <v>-33.84771876911908</v>
+        <v>-33.57267963602622</v>
       </c>
       <c r="F95">
-        <v>-2.455661349783127</v>
+        <v>-3.967060751295771</v>
       </c>
       <c r="G95">
-        <v>-1.739755731920589</v>
+        <v>-2.026925694179129</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-7.864214007175072</v>
       </c>
       <c r="E96">
-        <v>-35.72893291291149</v>
+        <v>-36.16574725145436</v>
       </c>
       <c r="F96">
-        <v>-2.74788783193832</v>
+        <v>-3.695324765216227</v>
       </c>
       <c r="G96">
-        <v>-2.240068547634026</v>
+        <v>-3.029299293650737</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-8.774483078995587</v>
       </c>
       <c r="E97">
-        <v>-38.43469839673153</v>
+        <v>-37.92639756750356</v>
       </c>
       <c r="F97">
-        <v>-2.553121259824698</v>
+        <v>-3.795742775253194</v>
       </c>
       <c r="G97">
-        <v>-3.033020346836878</v>
+        <v>-2.304528179829175</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-9.713199113517039</v>
       </c>
       <c r="E98">
-        <v>-40.81387033511839</v>
+        <v>-40.51222188875645</v>
       </c>
       <c r="F98">
-        <v>-2.55386761885462</v>
+        <v>-3.644731397722844</v>
       </c>
       <c r="G98">
-        <v>-3.064675783283389</v>
+        <v>-3.556424217686731</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-10.64476804647284</v>
       </c>
       <c r="E99">
-        <v>-43.61311031516776</v>
+        <v>-43.08145840971924</v>
       </c>
       <c r="F99">
-        <v>-2.463409898468914</v>
+        <v>-4.044443520595689</v>
       </c>
       <c r="G99">
-        <v>-3.730032536311652</v>
+        <v>-3.90814650741552</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-11.60612887614848</v>
       </c>
       <c r="E100">
-        <v>-45.36905328248599</v>
+        <v>-45.37892762005971</v>
       </c>
       <c r="F100">
-        <v>-2.552804823476828</v>
+        <v>-3.879659706626395</v>
       </c>
       <c r="G100">
-        <v>-4.046937818603925</v>
+        <v>-4.287750211676051</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-12.51310722537276</v>
       </c>
       <c r="E101">
-        <v>-47.71923619451274</v>
+        <v>-46.75657545419918</v>
       </c>
       <c r="F101">
-        <v>-2.427370946242719</v>
+        <v>-4.21570019745046</v>
       </c>
       <c r="G101">
-        <v>-4.271786761085685</v>
+        <v>-5.423701013111712</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-13.4947780263417</v>
       </c>
       <c r="E102">
-        <v>-49.57424179498576</v>
+        <v>-49.16109779008097</v>
       </c>
       <c r="F102">
-        <v>-2.551728774220591</v>
+        <v>-4.090195908987112</v>
       </c>
       <c r="G102">
-        <v>-4.711632462524333</v>
+        <v>-5.331343413657125</v>
       </c>
     </row>
   </sheetData>
